--- a/artfynd/A 32326-2024 artfynd.xlsx
+++ b/artfynd/A 32326-2024 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121070190</v>
+        <v>121070157</v>
       </c>
       <c r="B7" t="n">
-        <v>98049</v>
+        <v>107016</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,30 +1272,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721342</v>
+        <v>721393</v>
       </c>
       <c r="R7" t="n">
-        <v>6384092</v>
+        <v>6384187</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121070157</v>
+        <v>121070145</v>
       </c>
       <c r="B8" t="n">
-        <v>107016</v>
+        <v>108955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,46 +1392,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721393</v>
+        <v>721441</v>
       </c>
       <c r="R8" t="n">
-        <v>6384187</v>
+        <v>6384065</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1492,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121070145</v>
+        <v>121070190</v>
       </c>
       <c r="B9" t="n">
-        <v>108955</v>
+        <v>98049</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,41 +1495,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721441</v>
+        <v>721342</v>
       </c>
       <c r="R9" t="n">
-        <v>6384065</v>
+        <v>6384092</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 32326-2024 artfynd.xlsx
+++ b/artfynd/A 32326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121070159</v>
+        <v>121070136</v>
       </c>
       <c r="B2" t="n">
-        <v>98049</v>
+        <v>98059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721396</v>
+        <v>721427</v>
       </c>
       <c r="R2" t="n">
-        <v>6384212</v>
+        <v>6383992</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121070200</v>
+        <v>121070190</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219797</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721356</v>
+        <v>721342</v>
       </c>
       <c r="R3" t="n">
-        <v>6384078</v>
+        <v>6384092</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,11 +876,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom 10 m.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121070189</v>
+        <v>121070152</v>
       </c>
       <c r="B4" t="n">
-        <v>98046</v>
+        <v>98085</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>741</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721342</v>
+        <v>721406</v>
       </c>
       <c r="R4" t="n">
-        <v>6384092</v>
+        <v>6384098</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121070151</v>
+        <v>121070141</v>
       </c>
       <c r="B5" t="n">
-        <v>98046</v>
+        <v>108965</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,47 +1035,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721406</v>
+        <v>721511</v>
       </c>
       <c r="R5" t="n">
-        <v>6384098</v>
+        <v>6383960</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1144,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121070196</v>
+        <v>121070157</v>
       </c>
       <c r="B6" t="n">
-        <v>107016</v>
+        <v>107026</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,7 +1165,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1193,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721361</v>
+        <v>721393</v>
       </c>
       <c r="R6" t="n">
-        <v>6384080</v>
+        <v>6384187</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1260,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121070157</v>
+        <v>121070198</v>
       </c>
       <c r="B7" t="n">
-        <v>107016</v>
+        <v>108965</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,43 +1262,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721393</v>
+        <v>721356</v>
       </c>
       <c r="R7" t="n">
-        <v>6384187</v>
+        <v>6384078</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1376,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121070145</v>
+        <v>121070201</v>
       </c>
       <c r="B8" t="n">
-        <v>108955</v>
+        <v>107026</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,37 +1369,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721441</v>
+        <v>721349</v>
       </c>
       <c r="R8" t="n">
-        <v>6384065</v>
+        <v>6384067</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121070190</v>
+        <v>121070140</v>
       </c>
       <c r="B9" t="n">
-        <v>98049</v>
+        <v>108965</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,50 +1481,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721342</v>
+        <v>721427</v>
       </c>
       <c r="R9" t="n">
-        <v>6384092</v>
+        <v>6383992</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121070199</v>
+        <v>121070153</v>
       </c>
       <c r="B10" t="n">
-        <v>107016</v>
+        <v>108965</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,43 +1592,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721356</v>
+        <v>721410</v>
       </c>
       <c r="R10" t="n">
-        <v>6384078</v>
+        <v>6384104</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1715,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121070141</v>
+        <v>121070189</v>
       </c>
       <c r="B11" t="n">
-        <v>108955</v>
+        <v>98056</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,41 +1695,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721511</v>
+        <v>721342</v>
       </c>
       <c r="R11" t="n">
-        <v>6383960</v>
+        <v>6384092</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1822,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121070153</v>
+        <v>121070151</v>
       </c>
       <c r="B12" t="n">
-        <v>108955</v>
+        <v>98056</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,38 +1811,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721410</v>
+        <v>721406</v>
       </c>
       <c r="R12" t="n">
-        <v>6384104</v>
+        <v>6384098</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1929,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121070158</v>
+        <v>121070197</v>
       </c>
       <c r="B13" t="n">
-        <v>98046</v>
+        <v>107026</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,30 +1927,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1978,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721396</v>
+        <v>721361</v>
       </c>
       <c r="R13" t="n">
-        <v>6384212</v>
+        <v>6384080</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2045,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121070152</v>
+        <v>121070145</v>
       </c>
       <c r="B14" t="n">
-        <v>98075</v>
+        <v>108965</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,50 +2043,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>741</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721406</v>
+        <v>721441</v>
       </c>
       <c r="R14" t="n">
-        <v>6384098</v>
+        <v>6384065</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2161,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121070198</v>
+        <v>121070200</v>
       </c>
       <c r="B15" t="n">
-        <v>108955</v>
+        <v>98056</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,28 +2150,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
@@ -2237,6 +2223,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Inom 10 m.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121070136</v>
+        <v>121070162</v>
       </c>
       <c r="B16" t="n">
-        <v>98049</v>
+        <v>107026</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,30 +2271,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2317,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721427</v>
+        <v>721396</v>
       </c>
       <c r="R16" t="n">
-        <v>6383992</v>
+        <v>6384212</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2384,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121070201</v>
+        <v>121070158</v>
       </c>
       <c r="B17" t="n">
-        <v>107016</v>
+        <v>98056</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,30 +2387,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2433,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721349</v>
+        <v>721396</v>
       </c>
       <c r="R17" t="n">
-        <v>6384067</v>
+        <v>6384212</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2500,10 +2491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121070140</v>
+        <v>121070199</v>
       </c>
       <c r="B18" t="n">
-        <v>108955</v>
+        <v>107026</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,34 +2507,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721427</v>
+        <v>721356</v>
       </c>
       <c r="R18" t="n">
-        <v>6383992</v>
+        <v>6384078</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121070162</v>
+        <v>121070159</v>
       </c>
       <c r="B19" t="n">
-        <v>107016</v>
+        <v>98059</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,25 +2619,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">

--- a/artfynd/A 32326-2024 artfynd.xlsx
+++ b/artfynd/A 32326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121070136</v>
+        <v>121070189</v>
       </c>
       <c r="B2" t="n">
-        <v>98059</v>
+        <v>98056</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721427</v>
+        <v>721342</v>
       </c>
       <c r="R2" t="n">
-        <v>6383992</v>
+        <v>6384092</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121070190</v>
+        <v>121070151</v>
       </c>
       <c r="B3" t="n">
-        <v>98059</v>
+        <v>98056</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721342</v>
+        <v>721406</v>
       </c>
       <c r="R3" t="n">
-        <v>6384092</v>
+        <v>6384098</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121070152</v>
+        <v>121070198</v>
       </c>
       <c r="B4" t="n">
-        <v>98085</v>
+        <v>108965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,47 +919,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>741</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721406</v>
+        <v>721356</v>
       </c>
       <c r="R4" t="n">
-        <v>6384098</v>
+        <v>6384078</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121070141</v>
+        <v>121070162</v>
       </c>
       <c r="B5" t="n">
-        <v>108965</v>
+        <v>107026</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,34 +1030,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721511</v>
+        <v>721396</v>
       </c>
       <c r="R5" t="n">
-        <v>6383960</v>
+        <v>6384212</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121070157</v>
+        <v>121070136</v>
       </c>
       <c r="B6" t="n">
-        <v>107026</v>
+        <v>98059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,30 +1142,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721393</v>
+        <v>721427</v>
       </c>
       <c r="R6" t="n">
-        <v>6384187</v>
+        <v>6383992</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121070198</v>
+        <v>121070197</v>
       </c>
       <c r="B7" t="n">
-        <v>108965</v>
+        <v>107026</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,34 +1262,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721356</v>
+        <v>721361</v>
       </c>
       <c r="R7" t="n">
-        <v>6384078</v>
+        <v>6384080</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121070201</v>
+        <v>121070200</v>
       </c>
       <c r="B8" t="n">
-        <v>107026</v>
+        <v>98056</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,30 +1374,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220079</v>
+        <v>219797</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1402,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721349</v>
+        <v>721356</v>
       </c>
       <c r="R8" t="n">
-        <v>6384067</v>
+        <v>6384078</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,6 +1447,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Inom 10 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121070140</v>
+        <v>121070201</v>
       </c>
       <c r="B9" t="n">
-        <v>108965</v>
+        <v>107026</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1499,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721427</v>
+        <v>721349</v>
       </c>
       <c r="R9" t="n">
-        <v>6383992</v>
+        <v>6384067</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,7 +1599,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121070153</v>
+        <v>121070145</v>
       </c>
       <c r="B10" t="n">
         <v>108965</v>
@@ -1616,13 +1639,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721410</v>
+        <v>721441</v>
       </c>
       <c r="R10" t="n">
-        <v>6384104</v>
+        <v>6384065</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121070189</v>
+        <v>121070159</v>
       </c>
       <c r="B11" t="n">
-        <v>98056</v>
+        <v>98059</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,26 +1722,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219797</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1732,13 +1755,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721342</v>
+        <v>721396</v>
       </c>
       <c r="R11" t="n">
-        <v>6384092</v>
+        <v>6384212</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121070151</v>
+        <v>121070157</v>
       </c>
       <c r="B12" t="n">
-        <v>98056</v>
+        <v>107026</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,30 +1834,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1848,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721406</v>
+        <v>721393</v>
       </c>
       <c r="R12" t="n">
-        <v>6384098</v>
+        <v>6384187</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121070197</v>
+        <v>121070152</v>
       </c>
       <c r="B13" t="n">
-        <v>107026</v>
+        <v>98085</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,30 +1950,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220079</v>
+        <v>741</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1964,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721361</v>
+        <v>721406</v>
       </c>
       <c r="R13" t="n">
-        <v>6384080</v>
+        <v>6384098</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2031,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121070145</v>
+        <v>121070190</v>
       </c>
       <c r="B14" t="n">
-        <v>108965</v>
+        <v>98059</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,41 +2066,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721441</v>
+        <v>721342</v>
       </c>
       <c r="R14" t="n">
-        <v>6384065</v>
+        <v>6384092</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121070200</v>
+        <v>121070141</v>
       </c>
       <c r="B15" t="n">
-        <v>98056</v>
+        <v>108965</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,47 +2182,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721356</v>
+        <v>721511</v>
       </c>
       <c r="R15" t="n">
-        <v>6384078</v>
+        <v>6383960</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2223,11 +2246,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Inom 10 m.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121070162</v>
+        <v>121070199</v>
       </c>
       <c r="B16" t="n">
         <v>107026</v>
@@ -2294,7 +2312,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2308,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721396</v>
+        <v>721356</v>
       </c>
       <c r="R16" t="n">
-        <v>6384212</v>
+        <v>6384078</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2375,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121070158</v>
+        <v>121070153</v>
       </c>
       <c r="B17" t="n">
-        <v>98056</v>
+        <v>108965</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,47 +2405,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721396</v>
+        <v>721410</v>
       </c>
       <c r="R17" t="n">
-        <v>6384212</v>
+        <v>6384104</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2491,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121070199</v>
+        <v>121070140</v>
       </c>
       <c r="B18" t="n">
-        <v>107026</v>
+        <v>108965</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,43 +2516,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721356</v>
+        <v>721427</v>
       </c>
       <c r="R18" t="n">
-        <v>6384078</v>
+        <v>6383992</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121070159</v>
+        <v>121070158</v>
       </c>
       <c r="B19" t="n">
-        <v>98059</v>
+        <v>98056</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2623,26 +2623,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">

--- a/artfynd/A 32326-2024 artfynd.xlsx
+++ b/artfynd/A 32326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121070189</v>
+        <v>121070196</v>
       </c>
       <c r="B2" t="n">
-        <v>98056</v>
+        <v>107039</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721342</v>
+        <v>721361</v>
       </c>
       <c r="R2" t="n">
-        <v>6384092</v>
+        <v>6384080</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121070151</v>
+        <v>121070201</v>
       </c>
       <c r="B3" t="n">
-        <v>98056</v>
+        <v>107039</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,30 +803,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721406</v>
+        <v>721349</v>
       </c>
       <c r="R3" t="n">
-        <v>6384098</v>
+        <v>6384067</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121070198</v>
+        <v>121070136</v>
       </c>
       <c r="B4" t="n">
-        <v>108965</v>
+        <v>98072</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,38 +919,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721356</v>
+        <v>721427</v>
       </c>
       <c r="R4" t="n">
-        <v>6384078</v>
+        <v>6383992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121070162</v>
+        <v>121070157</v>
       </c>
       <c r="B5" t="n">
-        <v>107026</v>
+        <v>107039</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,7 +1058,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1063,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721396</v>
+        <v>721393</v>
       </c>
       <c r="R5" t="n">
-        <v>6384212</v>
+        <v>6384187</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1130,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121070136</v>
+        <v>121070158</v>
       </c>
       <c r="B6" t="n">
-        <v>98059</v>
+        <v>98069</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1179,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721427</v>
+        <v>721396</v>
       </c>
       <c r="R6" t="n">
-        <v>6383992</v>
+        <v>6384212</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1246,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121070197</v>
+        <v>121070190</v>
       </c>
       <c r="B7" t="n">
-        <v>107026</v>
+        <v>98072</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,30 +1267,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1295,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721361</v>
+        <v>721342</v>
       </c>
       <c r="R7" t="n">
-        <v>6384080</v>
+        <v>6384092</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121070200</v>
+        <v>121070140</v>
       </c>
       <c r="B8" t="n">
-        <v>98056</v>
+        <v>108978</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,47 +1383,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721356</v>
+        <v>721427</v>
       </c>
       <c r="R8" t="n">
-        <v>6384078</v>
+        <v>6383992</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,11 +1447,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Inom 10 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121070201</v>
+        <v>121070141</v>
       </c>
       <c r="B9" t="n">
-        <v>107026</v>
+        <v>108978</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,43 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721349</v>
+        <v>721511</v>
       </c>
       <c r="R9" t="n">
-        <v>6384067</v>
+        <v>6383960</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1599,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121070145</v>
+        <v>121070151</v>
       </c>
       <c r="B10" t="n">
-        <v>108965</v>
+        <v>98069</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,41 +1597,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721441</v>
+        <v>721406</v>
       </c>
       <c r="R10" t="n">
-        <v>6384065</v>
+        <v>6384098</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121070159</v>
+        <v>121070153</v>
       </c>
       <c r="B11" t="n">
-        <v>98059</v>
+        <v>108978</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,47 +1713,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721396</v>
+        <v>721410</v>
       </c>
       <c r="R11" t="n">
-        <v>6384212</v>
+        <v>6384104</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1822,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121070157</v>
+        <v>121070162</v>
       </c>
       <c r="B12" t="n">
-        <v>107026</v>
+        <v>107039</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,7 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1871,10 +1857,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721393</v>
+        <v>721396</v>
       </c>
       <c r="R12" t="n">
-        <v>6384187</v>
+        <v>6384212</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1938,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121070152</v>
+        <v>121070198</v>
       </c>
       <c r="B13" t="n">
-        <v>98085</v>
+        <v>108978</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,47 +1936,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>741</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721406</v>
+        <v>721356</v>
       </c>
       <c r="R13" t="n">
-        <v>6384098</v>
+        <v>6384078</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2054,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121070190</v>
+        <v>121070145</v>
       </c>
       <c r="B14" t="n">
-        <v>98059</v>
+        <v>108978</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,50 +2043,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721342</v>
+        <v>721441</v>
       </c>
       <c r="R14" t="n">
-        <v>6384092</v>
+        <v>6384065</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2170,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121070141</v>
+        <v>121070189</v>
       </c>
       <c r="B15" t="n">
-        <v>108965</v>
+        <v>98069</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,41 +2150,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721511</v>
+        <v>721342</v>
       </c>
       <c r="R15" t="n">
-        <v>6383960</v>
+        <v>6384092</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2277,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121070199</v>
+        <v>121070159</v>
       </c>
       <c r="B16" t="n">
-        <v>107026</v>
+        <v>98072</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,30 +2266,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2326,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721356</v>
+        <v>721396</v>
       </c>
       <c r="R16" t="n">
-        <v>6384078</v>
+        <v>6384212</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2393,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121070153</v>
+        <v>121070199</v>
       </c>
       <c r="B17" t="n">
-        <v>108965</v>
+        <v>107039</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,34 +2386,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721410</v>
+        <v>721356</v>
       </c>
       <c r="R17" t="n">
-        <v>6384104</v>
+        <v>6384078</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2500,10 +2486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121070140</v>
+        <v>121070152</v>
       </c>
       <c r="B18" t="n">
-        <v>108965</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,38 +2498,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>741</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Wahlenb.) K. Richt.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721427</v>
+        <v>721406</v>
       </c>
       <c r="R18" t="n">
-        <v>6383992</v>
+        <v>6384098</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2607,10 +2602,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121070158</v>
+        <v>121070200</v>
       </c>
       <c r="B19" t="n">
-        <v>98056</v>
+        <v>98069</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,7 +2637,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2656,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721396</v>
+        <v>721356</v>
       </c>
       <c r="R19" t="n">
-        <v>6384212</v>
+        <v>6384078</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2692,6 +2687,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inom 10 m.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 32326-2024 artfynd.xlsx
+++ b/artfynd/A 32326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121070196</v>
+        <v>121070152</v>
       </c>
       <c r="B2" t="n">
-        <v>107039</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>741</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721361</v>
+        <v>721406</v>
       </c>
       <c r="R2" t="n">
-        <v>6384080</v>
+        <v>6384098</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -791,62 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121070201</v>
+        <v>14217538</v>
       </c>
       <c r="B3" t="n">
-        <v>107039</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>100577</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tallgångbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cerylon impressum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Erichson, 1845</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+          <t>V Branden, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721349</v>
+        <v>721360</v>
       </c>
       <c r="R3" t="n">
-        <v>6384067</v>
+        <v>6383900</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2009-06-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2009-06-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På uppdrag av Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,33 +875,32 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+          <t>u bark döda tallar</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Naturcentrum AB</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Niklas Franc, Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121070136</v>
+        <v>121070592</v>
       </c>
       <c r="B4" t="n">
-        <v>98072</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>102118</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,9 +930,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721427</v>
+        <v>721317</v>
       </c>
       <c r="R4" t="n">
-        <v>6383992</v>
+        <v>6384139</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,6 +979,11 @@
           <t>2024-08-12</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Uppskrämd; flög tillbaka till första positionen då jag förfyttat mig 25 m från denna position.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1023,15 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121070157</v>
+        <v>121070178</v>
       </c>
       <c r="B5" t="n">
-        <v>107039</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220079</v>
+        <v>219719</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Säfferot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Seseli libanotis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) W. D. J. Koch</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721393</v>
+        <v>721325</v>
       </c>
       <c r="R5" t="n">
-        <v>6384187</v>
+        <v>6384042</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121070158</v>
+        <v>121070151</v>
       </c>
       <c r="B6" t="n">
-        <v>98069</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1188,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721396</v>
+        <v>721406</v>
       </c>
       <c r="R6" t="n">
-        <v>6384212</v>
+        <v>6384098</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,15 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121070190</v>
+        <v>121070158</v>
       </c>
       <c r="B7" t="n">
-        <v>98072</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,26 +1246,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1304,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721342</v>
+        <v>721396</v>
       </c>
       <c r="R7" t="n">
-        <v>6384092</v>
+        <v>6384212</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1371,50 +1346,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121070140</v>
+        <v>121070165</v>
       </c>
       <c r="B8" t="n">
-        <v>108978</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721427</v>
+        <v>721296</v>
       </c>
       <c r="R8" t="n">
-        <v>6383992</v>
+        <v>6384188</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1478,53 +1457,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121070141</v>
+        <v>121070189</v>
       </c>
       <c r="B9" t="n">
-        <v>108978</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721511</v>
+        <v>721342</v>
       </c>
       <c r="R9" t="n">
-        <v>6383960</v>
+        <v>6384092</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,15 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121070151</v>
+        <v>121070200</v>
       </c>
       <c r="B10" t="n">
-        <v>98069</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1634,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721406</v>
+        <v>721356</v>
       </c>
       <c r="R10" t="n">
-        <v>6384098</v>
+        <v>6384078</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1670,6 +1648,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inom 10 m.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,50 +1684,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121070153</v>
+        <v>121070136</v>
       </c>
       <c r="B11" t="n">
-        <v>108978</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721410</v>
+        <v>721427</v>
       </c>
       <c r="R11" t="n">
-        <v>6384104</v>
+        <v>6383992</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,37 +1795,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121070162</v>
+        <v>121070159</v>
       </c>
       <c r="B12" t="n">
-        <v>107039</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1924,50 +1906,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121070198</v>
+        <v>121070166</v>
       </c>
       <c r="B13" t="n">
-        <v>108978</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721356</v>
+        <v>721295</v>
       </c>
       <c r="R13" t="n">
-        <v>6384078</v>
+        <v>6384176</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2031,53 +2017,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121070145</v>
+        <v>121070183</v>
       </c>
       <c r="B14" t="n">
-        <v>108978</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gothem Magnuse 1:33 (2), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721441</v>
+        <v>721328</v>
       </c>
       <c r="R14" t="n">
-        <v>6384065</v>
+        <v>6384069</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,15 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121070189</v>
+        <v>121070187</v>
       </c>
       <c r="B15" t="n">
-        <v>98069</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,21 +2139,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219797</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2187,13 +2172,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721342</v>
+        <v>721331</v>
       </c>
       <c r="R15" t="n">
-        <v>6384092</v>
+        <v>6384080</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,15 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121070159</v>
+        <v>121070190</v>
       </c>
       <c r="B16" t="n">
-        <v>98072</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2269,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2303,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721396</v>
+        <v>721342</v>
       </c>
       <c r="R16" t="n">
-        <v>6384212</v>
+        <v>6384092</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2370,15 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121070199</v>
+        <v>121070157</v>
       </c>
       <c r="B17" t="n">
-        <v>107039</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2380,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2419,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721356</v>
+        <v>721393</v>
       </c>
       <c r="R17" t="n">
-        <v>6384078</v>
+        <v>6384187</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2486,42 +2461,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121070152</v>
+        <v>121070162</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>741</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2535,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721406</v>
+        <v>721396</v>
       </c>
       <c r="R18" t="n">
-        <v>6384098</v>
+        <v>6384212</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2602,42 +2572,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121070200</v>
+        <v>121070169</v>
       </c>
       <c r="B19" t="n">
-        <v>98069</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219797</v>
+        <v>220079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2651,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721356</v>
+        <v>721312</v>
       </c>
       <c r="R19" t="n">
-        <v>6384078</v>
+        <v>6384128</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2689,11 +2654,6 @@
           <t>2024-08-12</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Inom 10 m.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2720,6 +2680,2466 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121070170</v>
+      </c>
+      <c r="B20" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>721318</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6384118</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121070171</v>
+      </c>
+      <c r="B21" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>721317</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6384107</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121070175</v>
+      </c>
+      <c r="B22" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>721318</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6384108</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121070177</v>
+      </c>
+      <c r="B23" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>721328</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6384102</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121070179</v>
+      </c>
+      <c r="B24" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>721325</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6384042</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121070182</v>
+      </c>
+      <c r="B25" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>721328</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6384069</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Dessutom spridd.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121070188</v>
+      </c>
+      <c r="B26" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>721326</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6384085</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121070196</v>
+      </c>
+      <c r="B27" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>721361</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6384080</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121070199</v>
+      </c>
+      <c r="B28" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>721356</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6384078</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121070201</v>
+      </c>
+      <c r="B29" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>721349</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6384067</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121070203</v>
+      </c>
+      <c r="B30" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>721341</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6384050</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121070140</v>
+      </c>
+      <c r="B31" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>721427</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6383992</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121070141</v>
+      </c>
+      <c r="B32" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>721511</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6383960</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121070145</v>
+      </c>
+      <c r="B33" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>721441</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6384065</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121070153</v>
+      </c>
+      <c r="B34" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>721410</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6384104</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121070164</v>
+      </c>
+      <c r="B35" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>721296</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6384213</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121070185</v>
+      </c>
+      <c r="B36" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>721328</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6384069</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121070198</v>
+      </c>
+      <c r="B37" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>721356</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6384078</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121070167</v>
+      </c>
+      <c r="B38" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>721295</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6384176</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121070172</v>
+      </c>
+      <c r="B39" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>721317</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6384107</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121070174</v>
+      </c>
+      <c r="B40" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>721318</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6384108</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121070176</v>
+      </c>
+      <c r="B41" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>721328</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6384102</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121070163</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101796</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224938</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vanlig backruta</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Thalictrum simplex subsp. simplex</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gothem Magnuse 1:33 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>721296</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6384213</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, halvgammal tallskog, skärm av äldre träd(?)..</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32326-2024 artfynd.xlsx
+++ b/artfynd/A 32326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14217538</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070592</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070178</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070151</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070158</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070165</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070189</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,6 +1726,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070200</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070136</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070159</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2014,6 +2074,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070166</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2125,6 +2190,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070183</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2236,6 +2306,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070187</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2347,6 +2422,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070190</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2458,6 +2538,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070157</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2569,6 +2654,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070162</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2680,6 +2770,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070169</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2791,6 +2886,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070170</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2902,6 +3002,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070171</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3013,6 +3118,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070175</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3124,6 +3234,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070177</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3240,6 +3355,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070179</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3356,6 +3476,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070182</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3467,6 +3592,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070188</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3578,6 +3708,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070196</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3689,6 +3824,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070199</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3800,6 +3940,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070201</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3911,6 +4056,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070203</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4013,6 +4163,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070140</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4115,6 +4270,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070141</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4217,6 +4377,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070145</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4319,6 +4484,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070153</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4421,6 +4591,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070164</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4523,6 +4698,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070185</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4625,6 +4805,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070198</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4727,6 +4912,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070167</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4829,6 +5019,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070172</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4931,6 +5126,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070174</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5033,6 +5233,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070176</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5140,8 +5345,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121070163</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>